--- a/astro-site/public/dl/restaurant-financial-plan-templates/02-restaurant-break-even-calculator.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/02-restaurant-break-even-calculator.xlsx
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -338,6 +338,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -955,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1057,6 +1060,13 @@
       <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="57" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1153,7 @@
           <t>Monthly rent</t>
         </is>
       </c>
-      <c r="C6" s="57" t="n">
+      <c r="C6" s="58" t="n">
         <v>3000</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1153,15 +1163,15 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Total fixed labor cost (gross wages + employer payroll taxes)</t>
         </is>
       </c>
-      <c r="C7" s="57" t="n">
+      <c r="C7" s="58" t="n">
         <v>8800</v>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>per month — ≈ gross wages × 1.10 (more with benefits): the EMPLOYER cost, not gross pay</t>
         </is>
@@ -1173,7 +1183,7 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C8" s="57" t="n">
+      <c r="C8" s="58" t="n">
         <v>400</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1188,7 +1198,7 @@
           <t>Utilities (electricity, water, gas)</t>
         </is>
       </c>
-      <c r="C9" s="57" t="n">
+      <c r="C9" s="58" t="n">
         <v>1500</v>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1203,7 +1213,7 @@
           <t>Fixed marketing</t>
         </is>
       </c>
-      <c r="C10" s="57" t="n">
+      <c r="C10" s="58" t="n">
         <v>500</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1218,7 +1228,7 @@
           <t>Accounting / Bookkeeping</t>
         </is>
       </c>
-      <c r="C11" s="57" t="n">
+      <c r="C11" s="58" t="n">
         <v>300</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1242,7 +1252,7 @@
           <t>Other fixed costs</t>
         </is>
       </c>
-      <c r="C13" s="57" t="n">
+      <c r="C13" s="58" t="n">
         <v>500</v>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1257,23 +1267,23 @@
           <t>TOTAL OPERATING FIXED COSTS</t>
         </is>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="61">
         <f>SUM(C6:C11)+C13</f>
         <v>15000.0</v>
       </c>
     </row>
-    <row r="15" ht="24.5" customHeight="1">
+    <row r="15" ht="36.75" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Loan payment (debt service)</t>
         </is>
       </c>
-      <c r="C15" s="57" t="n">
+      <c r="C15" s="58" t="n">
         <v>800</v>
       </c>
-      <c r="D15" s="59" t="inlineStr">
-        <is>
-          <t>Copy it from the amortization schedule: file 07 "Lender &amp; Investor Summary", "Loan Schedule" tab</t>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>Monthly figure: copy the ANNUAL PAYMENT from file 07 "Lender &amp; Investor Summary", "Loan Schedule" tab, and divide it by 12.</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1303,7 @@
       <c r="C17" s="34" t="n">
         <v>0.35</v>
       </c>
-      <c r="D17" s="59" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>Food cost + delivery fees + other variable costs (30-40% typical). Does NOT include fixed labor.</t>
         </is>
@@ -1312,7 +1322,7 @@
           <t>Average check per guest (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="58" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1408,7 +1418,7 @@
           <t>Total operating fixed costs / month</t>
         </is>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="62">
         <f>Inputs!$C$14</f>
         <v>15000.0</v>
       </c>
@@ -1441,7 +1451,7 @@
           <t>BREAK-EVEN REVENUE / month (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="63">
         <f>IFERROR(Inputs!$C$14/(1-Inputs!$C$17),"Check the variable cost % (it cannot be 100%)")</f>
         <v>23076.923076923074</v>
       </c>
@@ -1452,7 +1462,7 @@
           <t>Break-even revenue / day (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="62">
         <f>IFERROR($C$8/Inputs!$C$21,"Enter the opening days")</f>
         <v>887.5739644970413</v>
       </c>
@@ -1495,7 +1505,7 @@
           <t>Average check needed (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="62">
         <f>IFERROR($C$9/$C$12,"Enter the expected covers/day")</f>
         <v>16.13770844540075</v>
       </c>
@@ -1514,7 +1524,7 @@
           <t>Cash break-even revenue / month (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C16" s="62">
+      <c r="C16" s="63">
         <f>IFERROR((Inputs!$C$14+Inputs!$C$15)/(1-Inputs!$C$17),"Check the variable cost % (it cannot be 100%)")</f>
         <v>24307.69230769231</v>
       </c>
@@ -1566,15 +1576,15 @@
         <f>IFERROR(ROUND($C$10*$F21,0),0)</f>
         <v>10.0</v>
       </c>
-      <c r="B21" s="63">
+      <c r="B21" s="64">
         <f>IFERROR($A21*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>5720.0</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="64">
         <f>IFERROR(Inputs!$C$14+$B21*Inputs!$C$17,0)</f>
         <v>17002.0</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D21" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1588,15 +1598,15 @@
         <f>IFERROR(ROUND($C$10*$F22,0),0)</f>
         <v>21.0</v>
       </c>
-      <c r="B22" s="63">
+      <c r="B22" s="64">
         <f>IFERROR($A22*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>12012.0</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="64">
         <f>IFERROR(Inputs!$C$14+$B22*Inputs!$C$17,0)</f>
         <v>19204.2</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D22" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1610,15 +1620,15 @@
         <f>IFERROR(ROUND($C$10*$F23,0),0)</f>
         <v>31.0</v>
       </c>
-      <c r="B23" s="63">
+      <c r="B23" s="64">
         <f>IFERROR($A23*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>17732.0</v>
       </c>
-      <c r="C23" s="63">
+      <c r="C23" s="64">
         <f>IFERROR(Inputs!$C$14+$B23*Inputs!$C$17,0)</f>
         <v>21206.2</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1632,15 +1642,15 @@
         <f>IFERROR(ROUND($C$10*$F24,0),0)</f>
         <v>41.0</v>
       </c>
-      <c r="B24" s="63">
+      <c r="B24" s="64">
         <f>IFERROR($A24*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>23452.0</v>
       </c>
-      <c r="C24" s="63">
+      <c r="C24" s="64">
         <f>IFERROR(Inputs!$C$14+$B24*Inputs!$C$17,0)</f>
         <v>23208.199999999997</v>
       </c>
-      <c r="D24" s="63">
+      <c r="D24" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1654,15 +1664,15 @@
         <f>IFERROR(ROUND($C$10*$F25,0),0)</f>
         <v>51.0</v>
       </c>
-      <c r="B25" s="63">
+      <c r="B25" s="64">
         <f>IFERROR($A25*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>29172.0</v>
       </c>
-      <c r="C25" s="63">
+      <c r="C25" s="64">
         <f>IFERROR(Inputs!$C$14+$B25*Inputs!$C$17,0)</f>
         <v>25210.199999999997</v>
       </c>
-      <c r="D25" s="63">
+      <c r="D25" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1676,15 +1686,15 @@
         <f>IFERROR(ROUND($C$10*$F26,0),0)</f>
         <v>62.0</v>
       </c>
-      <c r="B26" s="63">
+      <c r="B26" s="64">
         <f>IFERROR($A26*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>35464.0</v>
       </c>
-      <c r="C26" s="63">
+      <c r="C26" s="64">
         <f>IFERROR(Inputs!$C$14+$B26*Inputs!$C$17,0)</f>
         <v>27412.4</v>
       </c>
-      <c r="D26" s="63">
+      <c r="D26" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1698,15 +1708,15 @@
         <f>IFERROR(ROUND($C$10*$F27,0),0)</f>
         <v>72.0</v>
       </c>
-      <c r="B27" s="63">
+      <c r="B27" s="64">
         <f>IFERROR($A27*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>41184.0</v>
       </c>
-      <c r="C27" s="63">
+      <c r="C27" s="64">
         <f>IFERROR(Inputs!$C$14+$B27*Inputs!$C$17,0)</f>
         <v>29414.4</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1720,15 +1730,15 @@
         <f>IFERROR(ROUND($C$10*$F28,0),0)</f>
         <v>82.0</v>
       </c>
-      <c r="B28" s="63">
+      <c r="B28" s="64">
         <f>IFERROR($A28*Inputs!$C$20*Inputs!$C$21,0)</f>
         <v>46904.0</v>
       </c>
-      <c r="C28" s="63">
+      <c r="C28" s="64">
         <f>IFERROR(Inputs!$C$14+$B28*Inputs!$C$17,0)</f>
         <v>31416.399999999998</v>
       </c>
-      <c r="D28" s="63">
+      <c r="D28" s="64">
         <f>$C$8</f>
         <v>23076.923076923074</v>
       </c>
@@ -1821,13 +1831,13 @@
           <t>Average check (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C4" s="64" t="n">
+      <c r="C4" s="65" t="n">
         <v>18</v>
       </c>
-      <c r="D4" s="65" t="n">
+      <c r="D4" s="66" t="n">
         <v>22</v>
       </c>
-      <c r="E4" s="66" t="n">
+      <c r="E4" s="67" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1869,15 +1879,15 @@
           <t>Operating fixed costs / month (from "Inputs" C14)</t>
         </is>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="68">
         <f>Inputs!$C$14</f>
         <v>15000.0</v>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="69">
         <f>Inputs!$C$14</f>
         <v>15000.0</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="70">
         <f>Inputs!$C$14</f>
         <v>15000.0</v>
       </c>
@@ -1895,15 +1905,15 @@
           <t>Monthly revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="63">
         <f>C4*C5*Inputs!$C$21</f>
         <v>18720.0</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="63">
         <f>D4*D5*Inputs!$C$21</f>
         <v>31460.0</v>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="63">
         <f>E4*E5*Inputs!$C$21</f>
         <v>54600.0</v>
       </c>
@@ -1914,15 +1924,15 @@
           <t>Variable Costs</t>
         </is>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="63">
         <f>C10*C6</f>
         <v>7488.0</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="63">
         <f>D10*D6</f>
         <v>11011.0</v>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="63">
         <f>E10*E6</f>
         <v>16380.0</v>
       </c>
@@ -1933,15 +1943,15 @@
           <t>Contribution Margin</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="63">
         <f>C10-C11</f>
         <v>11232.0</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="63">
         <f>D10-D11</f>
         <v>20449.0</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="63">
         <f>E10-E11</f>
         <v>38220.0</v>
       </c>
@@ -1952,15 +1962,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="61">
         <f>C12-C7</f>
         <v>-3768.0</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="61">
         <f>D12-D7</f>
         <v>5449.0</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="61">
         <f>E12-E7</f>
         <v>23220.0</v>
       </c>
@@ -1971,15 +1981,15 @@
           <t>Loan payment (debt service)</t>
         </is>
       </c>
-      <c r="C14" s="70">
+      <c r="C14" s="71">
         <f>Inputs!$C$15</f>
         <v>800.0</v>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="71">
         <f>Inputs!$C$15</f>
         <v>800.0</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="71">
         <f>Inputs!$C$15</f>
         <v>800.0</v>
       </c>
@@ -1990,15 +2000,15 @@
           <t>RESULT AFTER DEBT SERVICE</t>
         </is>
       </c>
-      <c r="C15" s="70">
+      <c r="C15" s="71">
         <f>C13-C14</f>
         <v>-4568.0</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="71">
         <f>D13-D14</f>
         <v>4649.0</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="71">
         <f>E13-E14</f>
         <v>22420.0</v>
       </c>
